--- a/用卷/2006.xlsx
+++ b/用卷/2006.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0819FF-2E17-4B1F-8E9A-992C6BA76E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFB0C61-1823-4589-BD56-6E4B99D92DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
   <si>
     <t>年份</t>
   </si>
@@ -216,9 +216,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>特别说明:英语全国2卷不含听力部分</t>
-  </si>
-  <si>
     <t>全国1卷</t>
   </si>
   <si>
@@ -253,10 +250,6 @@
   </si>
   <si>
     <t>数学、英语为陕西卷,其他科目为全国1卷</t>
-  </si>
-  <si>
-    <t>全国12卷,北京卷,天津卷,上海卷,江苏卷,山东卷,广东卷,重庆卷,四川卷</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>文综、理综为全国1卷,其他科目为山东卷</t>
@@ -280,6 +273,14 @@
   </si>
   <si>
     <t>2006年普通高等学校招生全国统一考试用卷情况统计(语数英物化生政史地)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>特别说明:英语全国2卷不含听力部分;全国1卷又叫乙卷,全国2卷又叫甲卷</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国12卷,北京卷,天津卷,上海卷,江苏卷,广东卷,重庆卷,四川卷</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -791,7 +792,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -799,7 +800,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -827,7 +828,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>48</v>
@@ -865,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -877,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>54</v>
@@ -891,7 +892,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>48</v>
@@ -905,7 +906,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -919,11 +920,9 @@
         <v>12</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -933,7 +932,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D12" s="1"/>
     </row>
@@ -979,7 +978,7 @@
         <v>49</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -993,7 +992,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" s="4"/>
     </row>
@@ -1005,7 +1004,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1"/>
     </row>
@@ -1017,7 +1016,7 @@
         <v>19</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -1029,7 +1028,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D20" s="3"/>
     </row>
@@ -1041,7 +1040,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D21" s="1"/>
     </row>
@@ -1053,7 +1052,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D22" s="1"/>
     </row>
@@ -1077,7 +1076,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D24" s="1"/>
     </row>
@@ -1089,7 +1088,7 @@
         <v>25</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>59</v>
@@ -1117,9 +1116,7 @@
       <c r="C27" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
@@ -1129,7 +1126,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D28" s="5"/>
     </row>
@@ -1141,7 +1138,7 @@
         <v>29</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="3"/>
     </row>
@@ -1153,7 +1150,7 @@
         <v>30</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D30" s="1"/>
     </row>
@@ -1165,7 +1162,7 @@
         <v>31</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>53</v>
@@ -1179,7 +1176,7 @@
         <v>58</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D32" s="3"/>
     </row>
@@ -1191,7 +1188,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D33" s="1"/>
     </row>
@@ -1203,7 +1200,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D34" s="1"/>
     </row>
@@ -1215,7 +1212,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D35" s="3"/>
     </row>
@@ -1251,7 +1248,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
@@ -1262,7 +1259,7 @@
         <v>35</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1273,7 +1270,7 @@
         <v>19</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -1281,10 +1278,10 @@
         <v>42</v>
       </c>
       <c r="B42" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -1292,10 +1289,10 @@
         <v>43</v>
       </c>
       <c r="B43" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -1303,10 +1300,10 @@
         <v>44</v>
       </c>
       <c r="B44" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -1314,10 +1311,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -1325,10 +1322,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -1336,10 +1333,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/用卷/2006.xlsx
+++ b/用卷/2006.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFB0C61-1823-4589-BD56-6E4B99D92DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D72F5F2-3BBD-41D1-A775-5354919781F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -938,7 +938,7 @@
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
